--- a/AAII_Financials/Quarterly/FLG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FLG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>FLG</t>
   </si>
@@ -656,79 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -736,46 +740,49 @@
         <v>498000</v>
       </c>
       <c r="E8" s="3">
+        <v>498000</v>
+      </c>
+      <c r="F8" s="3">
         <v>554000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>481000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>432000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>411000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>480000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>381000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>281000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>439000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>326000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>980000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1012000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>482000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>294000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -821,8 +828,11 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -830,46 +840,49 @@
         <v>498000</v>
       </c>
       <c r="E10" s="3">
+        <v>498000</v>
+      </c>
+      <c r="F10" s="3">
         <v>554000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>481000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>432000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>411000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>480000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>381000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>281000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>439000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>326000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>980000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1012000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>482000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>294000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +900,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,8 +948,11 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -981,102 +998,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
-        <v>17000</v>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
         <v>17000</v>
       </c>
       <c r="G14" s="3">
+        <v>17000</v>
+      </c>
+      <c r="H14" s="3">
         <v>14000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>18000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>34000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>164000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2500000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>91000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-32000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1934000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-99000</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="E15" s="3">
         <v>35000</v>
       </c>
       <c r="F15" s="3">
-        <v>37000</v>
+        <v>35000</v>
       </c>
       <c r="G15" s="3">
         <v>37000</v>
       </c>
       <c r="H15" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I15" s="3">
         <v>39000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>45000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>44000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>46000</v>
       </c>
       <c r="M15" s="3">
         <v>46000</v>
       </c>
       <c r="N15" s="3">
-        <v>47000</v>
+        <v>46000</v>
       </c>
       <c r="O15" s="3">
         <v>47000</v>
       </c>
       <c r="P15" s="3">
+        <v>47000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>25000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1091,102 +1117,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E17" s="3">
         <v>411000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>433000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>442000</v>
       </c>
-      <c r="G17" s="3">
-        <v>472000</v>
-      </c>
       <c r="H17" s="3">
+        <v>423000</v>
+      </c>
+      <c r="I17" s="3">
         <v>446000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>602000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>563000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>638000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>571000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>481000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>585000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>515000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>392000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E18" s="3">
         <v>87000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>121000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-40000</v>
-      </c>
       <c r="H18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-35000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-122000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-182000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-357000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-132000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-155000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>395000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>497000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>90000</v>
       </c>
       <c r="Q18" s="3">
         <v>90000</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1204,102 +1237,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E20" s="3">
         <v>55000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>59000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>63000</v>
       </c>
-      <c r="G20" s="3">
-        <v>27000</v>
-      </c>
       <c r="H20" s="3">
+        <v>76000</v>
+      </c>
+      <c r="I20" s="3">
         <v>78000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>105000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>135000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>33000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>85000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>162000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>36000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>37000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>17000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E21" s="3">
         <v>67000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>97000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-74000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-182000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-268000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-346000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-171000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-271000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>406000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>507000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>98000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>95000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1345,102 +1385,111 @@
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E23" s="3">
         <v>32000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-41000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-81000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-121000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-238000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-335000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-424000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-381000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2817000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>268000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>492000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2007000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>184000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E24" s="3">
         <v>11000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-11000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-21000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-50000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-55000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-101000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-54000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-112000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>61000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>79000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1486,102 +1535,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E26" s="3">
         <v>21000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-36000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-70000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-188000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-280000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-323000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-327000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2705000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>207000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>413000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2006000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E27" s="3">
         <v>13000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-45000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-78000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-108000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-196000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-289000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-333000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-335000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2691000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>197000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>401000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1977000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1627,8 +1685,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1735,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1721,8 +1785,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1768,102 +1835,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-55000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-59000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-63000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-27000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-78000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-105000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-135000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-33000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-85000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-162000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-36000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-37000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E33" s="3">
         <v>21000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-36000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-70000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-188000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-280000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-323000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-327000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2705000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>207000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>413000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2006000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1909,107 +1985,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E35" s="3">
         <v>21000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-36000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-70000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-188000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-280000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-323000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-327000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2705000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>207000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>413000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2006000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2027,8 +2112,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2046,102 +2132,109 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5108000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7006000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5894000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8484000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8094000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12614000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15430000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23080000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18990000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12890000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11475000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6929000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15806000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22250000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2032000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E42" s="3">
         <v>21000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>26000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>23000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>19000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>40000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>129000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>148000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>138000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>184000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>171000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>179000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2187,8 +2280,11 @@
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2196,281 +2292,299 @@
         <v>8000</v>
       </c>
       <c r="E44" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F44" s="3">
         <v>11000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>21000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>15000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12000</v>
-      </c>
-      <c r="O44" s="3">
-        <v>13000</v>
       </c>
       <c r="P44" s="3">
         <v>13000</v>
       </c>
       <c r="Q44" s="3">
+        <v>13000</v>
+      </c>
+      <c r="R44" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E45" s="3">
         <v>273000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>303000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>317000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>304000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>312000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1970000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>417000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>445000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>461000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>444000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>419000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>395000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5731000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7620000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6579000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9441000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8839000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13513000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16809000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26956000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27398000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14477000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13270000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9495000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18603000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24142000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3766000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>16567000</v>
+      </c>
+      <c r="E47" s="3">
         <v>14570000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16062000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15904000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>15634000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13682000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10751000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11889000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12114000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10900000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10720000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9846000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8932000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8969000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10645000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>843000</v>
+        <v>472000</v>
       </c>
       <c r="E48" s="3">
+        <v>474000</v>
+      </c>
+      <c r="F48" s="3">
         <v>857000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>853000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>871000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>899000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>978000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1108000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1105000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1094000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1078000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1080000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1189000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>978000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>610000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E49" s="3">
         <v>356000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>381000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>407000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>433000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>459000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>488000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>519000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1679000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1682000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1736000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4222000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4154000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4194000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3746000</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2516,8 +2630,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2563,55 +2680,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4269000</v>
+        <v>4493000</v>
       </c>
       <c r="E52" s="3">
+        <v>4638000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3909000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3473000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3445000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3651000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4063000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4043000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3475000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3635000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3626000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3211000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3234000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3426000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2657,55 +2780,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>87714000</v>
+      </c>
+      <c r="E54" s="3">
         <v>87129000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87512000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>91668000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>92237000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97628000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>100160000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>114367000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119055000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>112900000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>114057000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>111230000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>118796000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>123706000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>90144000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2723,8 +2852,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2742,102 +2872,109 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>67521000</v>
+      </c>
+      <c r="E57" s="3">
         <v>66832000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>66000000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69152000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>69745000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>73906000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>75870000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>83013000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>79032000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>74858000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>81526000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>82675000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>88497000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>84800000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>58721000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4774000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5020000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7094000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2522000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2530000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3529000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2785000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>125000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5122000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11500000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1554000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>666000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>104000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>122000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2936000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2859,15 +2996,15 @@
       <c r="I59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>1298000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>814000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
@@ -2883,149 +3020,161 @@
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72336000</v>
+      </c>
+      <c r="E60" s="3">
         <v>71894000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>73133000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>71721000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>72320000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>77484000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>78706000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>84545000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>85142000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>86478000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>83130000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>83387000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>88641000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>84980000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>61694000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6604000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6600000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5540000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11120000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11134000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11143000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12139000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20738000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24283000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16113000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20713000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14488000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16922000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21670000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18654000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>633000</v>
+      </c>
+      <c r="E62" s="3">
         <v>514000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>631000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>718000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>687000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>847000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1096000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>512000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>975000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1324000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1330000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2362000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2173000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6274000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>858000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3071,8 +3220,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3118,8 +3270,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3165,55 +3320,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79573000</v>
+      </c>
+      <c r="E66" s="3">
         <v>79008000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>79368000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>83559000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>84141000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>89474000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>91992000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>105795000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>110400000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103915000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>105690000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>100237000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>107736000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>112924000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>81320000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3231,8 +3392,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3278,8 +3440,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3325,8 +3490,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3352,13 +3520,13 @@
         <v>504000</v>
       </c>
       <c r="K70" s="3">
+        <v>504000</v>
+      </c>
+      <c r="L70" s="3">
         <v>761000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1098000</v>
-      </c>
-      <c r="M70" s="3">
-        <v>503000</v>
       </c>
       <c r="N70" s="3">
         <v>503000</v>
@@ -3372,8 +3540,11 @@
       <c r="Q70" s="3">
         <v>503000</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>503000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3419,55 +3590,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-958000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-980000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-988000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1006000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-957000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-875000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-763000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-562000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-270000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>73000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>443000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3278000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3205000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2923000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1041000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3513,8 +3690,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3560,8 +3740,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3607,55 +3790,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7637000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7617000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7640000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7605000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7592000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7650000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7664000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8068000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7894000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7887000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7864000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10490000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10557000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10279000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8321000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3701,107 +3890,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E81" s="3">
         <v>21000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-36000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-70000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-188000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-280000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-323000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-327000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2705000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>207000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>413000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2006000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3819,55 +4017,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E83" s="3">
         <v>11000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>11000</v>
       </c>
       <c r="H83" s="3">
         <v>11000</v>
       </c>
       <c r="I83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J83" s="3">
         <v>10000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4000</v>
       </c>
       <c r="O83" s="3">
         <v>4000</v>
       </c>
       <c r="P83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3913,8 +4115,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3960,8 +4165,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4007,8 +4215,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4054,8 +4265,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4101,55 +4315,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>226000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-118000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-189000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>243000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>355000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-590000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>623000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1039000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>796000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-294000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>779000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1054000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4605000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3035000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>395000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4167,55 +4387,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>27000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>11000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4261,8 +4485,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4308,55 +4535,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2555000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1414000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1766000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>757000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>589000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-425000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4454000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9827000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-788000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1960000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1734000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1733000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-965000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>25105000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1581000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4374,19 +4607,20 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E96" s="3">
         <v>5000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>4000</v>
       </c>
       <c r="G96" s="3">
         <v>4000</v>
@@ -4395,34 +4629,37 @@
         <v>4000</v>
       </c>
       <c r="I96" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J96" s="3">
         <v>5000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M96" s="3">
         <v>8000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>122000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>125000</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q96" s="3">
         <v>8000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4468,8 +4705,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4515,8 +4755,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4562,55 +4805,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>424000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-188000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4159000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-612000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5420000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1897000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12669000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4693000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6020000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-247000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5435000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8212000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-839000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7793000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1568000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4656,51 +4905,57 @@
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1905000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1108000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2582000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>388000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4476000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2912000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7592000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4095000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6028000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1419000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4480000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8891000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6409000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20347000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>382000</v>
       </c>
     </row>
